--- a/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,6 +820,88 @@
       </c>
       <c r="M8" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>enemy_prism</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,129 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>enemy_minelayer</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>enemy_loader</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>enemy_siege_heavy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeUnit-攻城单位参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,252 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>enemy_sprayer</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>enemy_oil_crawler</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>enemy_corrosion_swarm</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>enemy_ln2_pump</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>enemy_deact_drone</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>enemy_settling_tank</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
